--- a/data/output/papertrail_test_survey_import.xlsx
+++ b/data/output/papertrail_test_survey_import.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA12"/>
+  <dimension ref="A1:AA13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1564,6 +1564,115 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0.0.0.0</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>R_papertrail_0001</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>paper</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/output/papertrail_test_survey_import.xlsx
+++ b/data/output/papertrail_test_survey_import.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA13"/>
+  <dimension ref="A1:AA15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1673,6 +1673,216 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.0.0.0</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>R_papertrail_0001</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>paper</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0.0.0.0</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>R_papertrail_0001</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>paper</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/output/papertrail_test_survey_import.xlsx
+++ b/data/output/papertrail_test_survey_import.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA15"/>
+  <dimension ref="A1:AA18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1883,6 +1883,261 @@
       </c>
       <c r="AA15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0.0.0.0</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>R_papertrail_0001</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>paper</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0.0.0.0</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>R_papertrail_0001</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>paper</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0.0.0.0</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>R_papertrail_0002</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>paper</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
